--- a/docs/training/files/basic_calendar_answer.xlsx
+++ b/docs/training/files/basic_calendar_answer.xlsx
@@ -72,12 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2A8"/>
+        <fgColor rgb="FFFFF2A8"/>
       </patternFill>
     </fill>
   </fills>
